--- a/analysis/tables/paper_tables.xlsx
+++ b/analysis/tables/paper_tables.xlsx
@@ -6,86 +6,962 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Dev-сводно" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full-сводно" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mood-сводно" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dev" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Full" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mood" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
+  <si>
+    <t xml:space="preserve">Сценарий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Описание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n₁/n₂</t>
+  </si>
   <si>
     <t xml:space="preserve">Метод</t>
   </si>
   <si>
-    <t xml:space="preserve">Сценариев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Значимых (p&lt;0.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Средняя макс. отн. ошибка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Среднее время, с</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Всего циклов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass, %</t>
+    <t xml:space="preserve">SW p₁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW p₂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p (критерий)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean₁/mean₂ · med₁/med₂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">макс. отн. ошибка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">время, с</t>
+  </si>
+  <si>
+    <t xml:space="preserve">циклы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормальные, равные (30/25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/25</t>
   </si>
   <si>
     <t xml:space="preserve">Уэлча</t>
   </si>
   <si>
+    <t xml:space="preserve">0.544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103 / 98.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">да</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 441 792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормальные, смещение среднего (8/8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 / 0.3764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">917 504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормальные, неравные дисперсии (60/60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60/60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.05 / 57.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 490 368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормальные, неравные n (200/30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200/30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9384 / 1.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6e-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 407 872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормальные, n = 3/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4154 / 1.259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">786 432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Логнормальные (40/40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40/40</t>
+  </si>
+  <si>
     <t xml:space="preserve">Муд</t>
   </si>
   <si>
-    <t xml:space="preserve">Все</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кейсов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Все pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сегментов (см.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">да</t>
+    <t xml:space="preserve">0.245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9e-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.9995 / m₂ 1.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 849 664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гамма, shape = 2 (40/40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 1.185 / m₂ 1.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 373 952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Экспоненциальные (50/50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50/50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 1.472 / m₂ 2.527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 636 096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Равномерные (35/35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35/35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.5535 / m₂ 1.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 325 376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t₃, тяжёлый хвост (45/45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45/45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.09944 / m₂ 0.8871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бимодальная смесь (40/40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.2816 / m₂ 1.138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дискретные 1:5 (50/50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 3 / m₂ 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3e-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупные нормальные (1000/1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000/1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0e-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.956 / 10.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8e-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 772 608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Граница n = 11/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3084 / 0.9444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Константная группа (20/20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— (SW), ошибка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t₂, n = 3/3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03198 / 2.983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6e-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">655 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Полунормальные (38/38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38/38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.5857 / m₂ 0.9715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пуассоновские счёта (60/60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 3 / m₂ 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8e-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 422 528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Равные средние, разные sd (25/25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01507 / 0.485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разность средних (32/32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32/32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01499 / 1.149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сегментов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1186</t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">Значимых по M̂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Значимых по точной медиане</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЛП (наш да, истинная нет)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЛО (наш нет, истинная да)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согласие решений, %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Средняя |разность p|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Макс. |разность p|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Совпало 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нет</t>
+    <t xml:space="preserve">704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">med₁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">med₂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M̂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p (наш, M̂)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p (истинная медиана)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">разность p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.02918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7e-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8e-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.004256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.002261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.03702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.3e-04</t>
   </si>
 </sst>
 </file>
@@ -93,19 +969,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,11 +998,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,105 +1290,816 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="13.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="9.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="32.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="9.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="9.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="16.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="7.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="12.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="24.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00000000000023</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38273024</v>
-      </c>
-      <c r="G2" t="n">
-        <v>100</v>
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0000000000000711</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F3" t="n">
-        <v>48365568</v>
-      </c>
-      <c r="G3" t="n">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="n">
-        <v>19</v>
-      </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.000000000000155</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="F4" t="n">
-        <v>86638592</v>
-      </c>
-      <c r="G4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" t="s">
         <v>100</v>
+      </c>
+      <c r="J10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" t="s">
+        <v>116</v>
+      </c>
+      <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" t="s">
+        <v>129</v>
+      </c>
+      <c r="H14" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" t="s">
+        <v>131</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>132</v>
+      </c>
+      <c r="L14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>141</v>
+      </c>
+      <c r="L15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H16" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" t="s">
+        <v>147</v>
+      </c>
+      <c r="J16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>148</v>
+      </c>
+      <c r="L16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" t="s">
+        <v>154</v>
+      </c>
+      <c r="H17" t="s">
+        <v>155</v>
+      </c>
+      <c r="I17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" t="s">
+        <v>157</v>
+      </c>
+      <c r="L17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H19" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J19" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>173</v>
+      </c>
+      <c r="L19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" t="s">
+        <v>179</v>
+      </c>
+      <c r="G20" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" t="s">
+        <v>181</v>
+      </c>
+      <c r="I20" t="s">
+        <v>182</v>
+      </c>
+      <c r="J20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" t="s">
+        <v>183</v>
+      </c>
+      <c r="L20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" t="s">
+        <v>188</v>
+      </c>
+      <c r="G21" t="s">
+        <v>189</v>
+      </c>
+      <c r="H21" t="s">
+        <v>190</v>
+      </c>
+      <c r="I21" t="s">
+        <v>191</v>
+      </c>
+      <c r="J21" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>141</v>
+      </c>
+      <c r="L21" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -535,52 +2113,131 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="32.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="16.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="24.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="10.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.0000000000000347</v>
-      </c>
-      <c r="D2" t="n">
-        <v>759</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3014656</v>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -595,72 +2252,655 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="18.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="15.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="32.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="6.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="6.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="12.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>22</v>
+      <c r="C1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.571</v>
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H2" t="s">
+        <v>210</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>211</v>
+      </c>
+      <c r="J2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G4" t="s">
+        <v>223</v>
+      </c>
+      <c r="H4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F5" t="s">
+        <v>229</v>
+      </c>
+      <c r="G5" t="s">
+        <v>230</v>
+      </c>
+      <c r="H5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" t="s">
+        <v>236</v>
+      </c>
+      <c r="F6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" t="s">
+        <v>245</v>
+      </c>
+      <c r="J7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" t="s">
+        <v>250</v>
+      </c>
+      <c r="G8" t="s">
+        <v>208</v>
+      </c>
+      <c r="H8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" t="s">
+        <v>251</v>
+      </c>
+      <c r="J8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" t="s">
+        <v>257</v>
+      </c>
+      <c r="J9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" t="s">
+        <v>262</v>
+      </c>
+      <c r="G10" t="s">
+        <v>263</v>
+      </c>
+      <c r="H10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" t="s">
+        <v>168</v>
+      </c>
+      <c r="J10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" t="s">
+        <v>266</v>
+      </c>
+      <c r="E11" t="s">
+        <v>267</v>
+      </c>
+      <c r="F11" t="s">
+        <v>268</v>
+      </c>
+      <c r="G11" t="s">
+        <v>269</v>
+      </c>
+      <c r="H11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" t="s">
+        <v>273</v>
+      </c>
+      <c r="G12" t="s">
+        <v>273</v>
+      </c>
+      <c r="H12" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D13" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" t="s">
+        <v>274</v>
+      </c>
+      <c r="G13" t="s">
+        <v>208</v>
+      </c>
+      <c r="H13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" t="s">
+        <v>121</v>
+      </c>
+      <c r="J13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D14" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F14" t="s">
+        <v>278</v>
+      </c>
+      <c r="G14" t="s">
+        <v>279</v>
+      </c>
+      <c r="H14" t="s">
+        <v>280</v>
+      </c>
+      <c r="I14" t="s">
+        <v>281</v>
+      </c>
+      <c r="J14" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" t="s">
+        <v>283</v>
+      </c>
+      <c r="D15" t="s">
+        <v>284</v>
+      </c>
+      <c r="E15" t="s">
+        <v>285</v>
+      </c>
+      <c r="F15" t="s">
+        <v>243</v>
+      </c>
+      <c r="G15" t="s">
+        <v>286</v>
+      </c>
+      <c r="H15" t="s">
+        <v>287</v>
+      </c>
+      <c r="I15" t="s">
+        <v>288</v>
+      </c>
+      <c r="J15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F16" t="s">
+        <v>293</v>
+      </c>
+      <c r="G16" t="s">
+        <v>237</v>
+      </c>
+      <c r="H16" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D17" t="s">
+        <v>295</v>
+      </c>
+      <c r="E17" t="s">
+        <v>296</v>
+      </c>
+      <c r="F17" t="s">
+        <v>297</v>
+      </c>
+      <c r="G17" t="s">
+        <v>273</v>
+      </c>
+      <c r="H17" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" t="s">
+        <v>298</v>
+      </c>
+      <c r="J17" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E18" t="s">
+        <v>300</v>
+      </c>
+      <c r="F18" t="s">
+        <v>274</v>
+      </c>
+      <c r="G18" t="s">
+        <v>301</v>
+      </c>
+      <c r="H18" t="s">
+        <v>170</v>
+      </c>
+      <c r="I18" t="s">
+        <v>302</v>
+      </c>
+      <c r="J18" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" t="s">
+        <v>304</v>
+      </c>
+      <c r="D19" t="s">
+        <v>305</v>
+      </c>
+      <c r="E19" t="s">
+        <v>306</v>
+      </c>
+      <c r="F19" t="s">
+        <v>297</v>
+      </c>
+      <c r="G19" t="s">
+        <v>307</v>
+      </c>
+      <c r="H19" t="s">
+        <v>308</v>
+      </c>
+      <c r="I19" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" t="s">
+        <v>310</v>
+      </c>
+      <c r="D20" t="s">
+        <v>311</v>
+      </c>
+      <c r="E20" t="s">
+        <v>312</v>
+      </c>
+      <c r="F20" t="s">
+        <v>313</v>
+      </c>
+      <c r="G20" t="s">
+        <v>314</v>
+      </c>
+      <c r="H20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/tables/paper_tables.xlsx
+++ b/analysis/tables/paper_tables.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="385">
   <si>
     <t xml:space="preserve">Сценарий</t>
   </si>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">да</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79</t>
+    <t xml:space="preserve">0.42</t>
   </si>
   <si>
     <t xml:space="preserve">1 441 792</t>
@@ -109,498 +109,504 @@
     <t xml:space="preserve">0.2 / 0.3764</t>
   </si>
   <si>
+    <t xml:space="preserve">1.5e-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">917 504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормальные, неравные дисперсии (60/60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60/60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.05 / 57.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 490 368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормальные, неравные n (200/30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200/30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9384 / 1.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6e-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 670 016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормальные, n = 3/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4154 / 1.259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">786 432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Логнормальные (40/40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40/40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Муд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.9995 / m₂ 1.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 373 952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гамма, shape = 2 (40/40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 1.185 / m₂ 1.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Экспоненциальные (50/50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50/50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 1.472 / m₂ 2.527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 422 528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Равномерные (35/35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35/35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.5535 / m₂ 1.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 849 664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t₃, тяжёлый хвост (45/45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45/45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.09944 / m₂ 0.8871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бимодальная смесь (40/40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.2816 / m₂ 1.138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дискретные 1:5 (50/50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 3 / m₂ 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3e-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупные нормальные (1000/1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000/1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0e-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.956 / 10.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8e-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 607 616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Граница n = 11/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3084 / 0.9444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Константная группа (20/20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— (SW), ошибка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t₂, n = 3/3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03198 / 2.983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6e-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">655 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Полунормальные (38/38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38/38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 0.5857 / m₂ 0.9715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пуассоновские счёта (60/60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m₁ 3 / m₂ 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8e-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Равные средние, разные sd (25/25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01507 / 0.485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разность средних (32/32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32/32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01499 / 1.149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сегментов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.5e-14</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">917 504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нормальные, неравные дисперсии (60/60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60/60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.05 / 57.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 490 368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нормальные, неравные n (200/30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200/30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9384 / 1.114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6e-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 407 872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нормальные, n = 3/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.4154 / 1.259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">786 432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Логнормальные (40/40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40/40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Муд</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9e-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 0.9995 / m₂ 1.996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 849 664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гамма, shape = 2 (40/40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 1.185 / m₂ 1.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 373 952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспоненциальные (50/50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50/50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0e-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3e-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 1.472 / m₂ 2.527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 636 096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Равномерные (35/35)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35/35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 0.5535 / m₂ 1.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 325 376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t₃, тяжёлый хвост (45/45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45/45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 0.09944 / m₂ 0.8871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бимодальная смесь (40/40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2e-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 0.2816 / m₂ 1.138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дискретные 1:5 (50/50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3e-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 3 / m₂ 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3e-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Крупные нормальные (1000/1000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000/1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0e-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.956 / 10.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8e-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 772 608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Граница n = 11/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3084 / 0.9444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Константная группа (20/20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">— (SW), ошибка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t₂, n = 3/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03198 / 2.983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6e-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">655 360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Полунормальные (38/38)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38/38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 0.5857 / m₂ 0.9715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пуассоновские счёта (60/60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9e-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m₁ 3 / m₂ 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8e-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 422 528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Равные средние, разные sd (25/25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01507 / 0.485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Разность средних (32/32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32/32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2e-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01499 / 1.149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сегментов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
     <t xml:space="preserve">704</t>
   </si>
   <si>
@@ -631,28 +637,46 @@
     <t xml:space="preserve">разность p</t>
   </si>
   <si>
+    <t xml:space="preserve">сред. p (наш, M̂), 1000 реплик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сред. p (истинный), 1000 реплик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дельта mean(p)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% согласованности (1000 реплик)</t>
+  </si>
+  <si>
     <t xml:space="preserve">103.5</t>
   </si>
   <si>
     <t xml:space="preserve">96.01</t>
   </si>
   <si>
-    <t xml:space="preserve">99.76</t>
+    <t xml:space="preserve">100.1</t>
   </si>
   <si>
     <t xml:space="preserve">19</t>
   </si>
   <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.060</t>
+    <t xml:space="preserve">8</t>
   </si>
   <si>
     <t xml:space="preserve">0.031</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.02918</t>
+    <t xml:space="preserve">0.5165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6</t>
   </si>
   <si>
     <t xml:space="preserve">-0.2008</t>
@@ -661,7 +685,7 @@
     <t xml:space="preserve">0.4739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1366</t>
+    <t xml:space="preserve">0.1116</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
@@ -676,22 +700,46 @@
     <t xml:space="preserve">0.3046</t>
   </si>
   <si>
+    <t xml:space="preserve">0.589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">48.44</t>
   </si>
   <si>
     <t xml:space="preserve">59.61</t>
   </si>
   <si>
-    <t xml:space="preserve">54.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3e-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7e-04</t>
+    <t xml:space="preserve">50.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.6e-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8</t>
   </si>
   <si>
     <t xml:space="preserve">0.8546</t>
@@ -700,223 +748,355 @@
     <t xml:space="preserve">1.237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89</t>
+    <t xml:space="preserve">0.9267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.8e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4e-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7e-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.02628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8e-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4443</t>
   </si>
   <si>
     <t xml:space="preserve">18</t>
   </si>
   <si>
-    <t xml:space="preserve">0.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2e-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8e-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.527</t>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.004849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6e-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7316</t>
   </si>
   <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.004256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.002261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3e-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5e-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1e-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5</t>
+    <t xml:space="preserve">-0.155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.714</t>
   </si>
   <si>
     <t xml:space="preserve">45</t>
@@ -928,22 +1108,40 @@
     <t xml:space="preserve">6.1e-06</t>
   </si>
   <si>
+    <t xml:space="preserve">0.00686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.1308</t>
   </si>
   <si>
     <t xml:space="preserve">-0.3959</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.1325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4291</t>
+    <t xml:space="preserve">-0.0299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2</t>
   </si>
   <si>
     <t xml:space="preserve">-0.03702</t>
@@ -952,16 +1150,25 @@
     <t xml:space="preserve">1.017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.3e-04</t>
+    <t xml:space="preserve">0.4434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.8e-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2</t>
   </si>
 </sst>
 </file>
@@ -1605,42 +1812,42 @@
         <v>82</v>
       </c>
       <c r="L8" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
         <v>84</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
       </c>
       <c r="D9" t="s">
         <v>67</v>
       </c>
       <c r="E9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" t="s">
         <v>87</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>88</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>89</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>90</v>
-      </c>
-      <c r="I9" t="s">
-        <v>91</v>
       </c>
       <c r="J9" t="s">
         <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="L9" t="s">
         <v>92</v>
@@ -1678,56 +1885,56 @@
         <v>21</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="L10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
         <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J11" t="s">
         <v>21</v>
       </c>
       <c r="K11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L11" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
         <v>66</v>
@@ -1739,127 +1946,127 @@
         <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J12" t="s">
         <v>21</v>
       </c>
       <c r="K12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L12" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
         <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F13" t="s">
         <v>77</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J13" t="s">
         <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J14" t="s">
         <v>21</v>
       </c>
       <c r="K14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I15" t="s">
         <v>61</v>
@@ -1868,7 +2075,7 @@
         <v>21</v>
       </c>
       <c r="K15" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="L15" t="s">
         <v>33</v>
@@ -1876,124 +2083,124 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J16" t="s">
         <v>21</v>
       </c>
       <c r="K16" t="s">
+        <v>149</v>
+      </c>
+      <c r="L16" t="s">
         <v>148</v>
-      </c>
-      <c r="L16" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J17" t="s">
         <v>21</v>
       </c>
       <c r="K17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D18" t="s">
         <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F18" t="s">
         <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J18" t="s">
         <v>21</v>
       </c>
       <c r="K18" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="L18" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
@@ -2002,28 +2209,28 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J19" t="s">
         <v>21</v>
       </c>
       <c r="K19" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="L19" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
@@ -2096,7 +2303,7 @@
         <v>21</v>
       </c>
       <c r="K21" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s">
         <v>23</v>
@@ -2150,7 +2357,7 @@
         <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2">
@@ -2173,13 +2380,13 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H2" t="s">
         <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
@@ -2199,45 +2406,45 @@
         <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="G3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H3" t="s">
         <v>33</v>
       </c>
       <c r="I3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2261,6 +2468,10 @@
     <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="12.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="14.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="24.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2271,28 +2482,40 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J1" t="s">
-        <v>204</v>
+        <v>206</v>
+      </c>
+      <c r="K1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L1" t="s">
+        <v>208</v>
+      </c>
+      <c r="M1" t="s">
+        <v>209</v>
+      </c>
+      <c r="N1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="2">
@@ -2303,28 +2526,40 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="I2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J2" t="s">
-        <v>212</v>
+        <v>148</v>
+      </c>
+      <c r="K2" t="s">
+        <v>217</v>
+      </c>
+      <c r="L2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M2" t="s">
+        <v>219</v>
+      </c>
+      <c r="N2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="3">
@@ -2335,28 +2570,40 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="I3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J3" t="s">
-        <v>219</v>
+        <v>227</v>
+      </c>
+      <c r="K3" t="s">
+        <v>228</v>
+      </c>
+      <c r="L3" t="s">
+        <v>229</v>
+      </c>
+      <c r="M3" t="s">
+        <v>230</v>
+      </c>
+      <c r="N3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="4">
@@ -2367,28 +2614,40 @@
         <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D4" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="G4" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="H4" t="s">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s">
         <v>77</v>
       </c>
       <c r="J4" t="s">
-        <v>225</v>
+        <v>237</v>
+      </c>
+      <c r="K4" t="s">
+        <v>238</v>
+      </c>
+      <c r="L4" t="s">
+        <v>239</v>
+      </c>
+      <c r="M4" t="s">
+        <v>240</v>
+      </c>
+      <c r="N4" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="5">
@@ -2399,28 +2658,40 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="F5" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="G5" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="H5" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="I5" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="J5" t="s">
-        <v>233</v>
+        <v>148</v>
+      </c>
+      <c r="K5" t="s">
+        <v>247</v>
+      </c>
+      <c r="L5" t="s">
+        <v>248</v>
+      </c>
+      <c r="M5" t="s">
+        <v>249</v>
+      </c>
+      <c r="N5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="6">
@@ -2431,28 +2702,40 @@
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="D6" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G6" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="H6" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="I6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J6" t="s">
-        <v>239</v>
+        <v>256</v>
+      </c>
+      <c r="K6" t="s">
+        <v>257</v>
+      </c>
+      <c r="L6" t="s">
+        <v>258</v>
+      </c>
+      <c r="M6" t="s">
+        <v>259</v>
+      </c>
+      <c r="N6" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="7">
@@ -2463,28 +2746,40 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="F7" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="G7" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="H7" t="s">
         <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="J7" t="s">
-        <v>246</v>
+        <v>267</v>
+      </c>
+      <c r="K7" t="s">
+        <v>268</v>
+      </c>
+      <c r="L7" t="s">
+        <v>269</v>
+      </c>
+      <c r="M7" t="s">
+        <v>270</v>
+      </c>
+      <c r="N7" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="8">
@@ -2495,60 +2790,84 @@
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="D8" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="F8" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="G8" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H8" t="s">
         <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="J8" t="s">
-        <v>252</v>
+        <v>277</v>
+      </c>
+      <c r="K8" t="s">
+        <v>278</v>
+      </c>
+      <c r="L8" t="s">
+        <v>279</v>
+      </c>
+      <c r="M8" t="s">
+        <v>280</v>
+      </c>
+      <c r="N8" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
         <v>84</v>
       </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="D9" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="E9" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="F9" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="G9" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I9" t="s">
-        <v>257</v>
+        <v>88</v>
       </c>
       <c r="J9" t="s">
-        <v>258</v>
+        <v>148</v>
+      </c>
+      <c r="K9" t="s">
+        <v>287</v>
+      </c>
+      <c r="L9" t="s">
+        <v>288</v>
+      </c>
+      <c r="M9" t="s">
+        <v>289</v>
+      </c>
+      <c r="N9" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -2559,284 +2878,392 @@
         <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="E10" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="F10" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G10" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="H10" t="s">
         <v>98</v>
       </c>
       <c r="I10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J10" t="s">
-        <v>264</v>
+        <v>295</v>
+      </c>
+      <c r="K10" t="s">
+        <v>296</v>
+      </c>
+      <c r="L10" t="s">
+        <v>297</v>
+      </c>
+      <c r="M10" t="s">
+        <v>298</v>
+      </c>
+      <c r="N10" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="D11" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="E11" t="s">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="F11" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="G11" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="H11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I11" t="s">
         <v>78</v>
       </c>
       <c r="J11" t="s">
-        <v>270</v>
+        <v>305</v>
+      </c>
+      <c r="K11" t="s">
+        <v>306</v>
+      </c>
+      <c r="L11" t="s">
+        <v>307</v>
+      </c>
+      <c r="M11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N11" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>271</v>
+        <v>310</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="F12" t="s">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="G12" t="s">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="H12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J12" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="K12" t="s">
+        <v>314</v>
+      </c>
+      <c r="L12" t="s">
+        <v>315</v>
+      </c>
+      <c r="M12" t="s">
+        <v>316</v>
+      </c>
+      <c r="N12" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D13" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F13" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="G13" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J13" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="K13" t="s">
+        <v>318</v>
+      </c>
+      <c r="L13" t="s">
+        <v>319</v>
+      </c>
+      <c r="M13" t="s">
+        <v>320</v>
+      </c>
+      <c r="N13" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="E14" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="F14" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="G14" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="H14" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="I14" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="J14" t="s">
-        <v>282</v>
+        <v>329</v>
+      </c>
+      <c r="K14" t="s">
+        <v>330</v>
+      </c>
+      <c r="L14" t="s">
+        <v>331</v>
+      </c>
+      <c r="M14" t="s">
+        <v>332</v>
+      </c>
+      <c r="N14" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="E15" t="s">
-        <v>285</v>
+        <v>336</v>
       </c>
       <c r="F15" t="s">
-        <v>243</v>
+        <v>337</v>
       </c>
       <c r="G15" t="s">
-        <v>286</v>
+        <v>215</v>
       </c>
       <c r="H15" t="s">
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="I15" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="J15" t="s">
-        <v>289</v>
+        <v>148</v>
+      </c>
+      <c r="K15" t="s">
+        <v>339</v>
+      </c>
+      <c r="L15" t="s">
+        <v>340</v>
+      </c>
+      <c r="M15" t="s">
+        <v>341</v>
+      </c>
+      <c r="N15" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>290</v>
+        <v>343</v>
       </c>
       <c r="D16" t="s">
-        <v>291</v>
+        <v>344</v>
       </c>
       <c r="E16" t="s">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="F16" t="s">
-        <v>293</v>
+        <v>346</v>
       </c>
       <c r="G16" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="H16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J16" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="K16" t="s">
+        <v>347</v>
+      </c>
+      <c r="L16" t="s">
+        <v>348</v>
+      </c>
+      <c r="M16" t="s">
+        <v>349</v>
+      </c>
+      <c r="N16" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>350</v>
       </c>
       <c r="D17" t="s">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="E17" t="s">
-        <v>296</v>
+        <v>352</v>
       </c>
       <c r="F17" t="s">
-        <v>297</v>
+        <v>353</v>
       </c>
       <c r="G17" t="s">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="H17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" t="s">
-        <v>298</v>
+        <v>354</v>
       </c>
       <c r="J17" t="s">
-        <v>299</v>
+        <v>355</v>
+      </c>
+      <c r="K17" t="s">
+        <v>356</v>
+      </c>
+      <c r="L17" t="s">
+        <v>357</v>
+      </c>
+      <c r="M17" t="s">
+        <v>358</v>
+      </c>
+      <c r="N17" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="F18" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="G18" t="s">
-        <v>301</v>
+        <v>361</v>
       </c>
       <c r="H18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="J18" t="s">
-        <v>303</v>
+        <v>363</v>
+      </c>
+      <c r="K18" t="s">
+        <v>364</v>
+      </c>
+      <c r="L18" t="s">
+        <v>365</v>
+      </c>
+      <c r="M18" t="s">
+        <v>366</v>
+      </c>
+      <c r="N18" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="19">
@@ -2847,28 +3274,40 @@
         <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="D19" t="s">
-        <v>305</v>
+        <v>369</v>
       </c>
       <c r="E19" t="s">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="F19" t="s">
-        <v>297</v>
+        <v>371</v>
       </c>
       <c r="G19" t="s">
-        <v>307</v>
+        <v>264</v>
       </c>
       <c r="H19" t="s">
-        <v>308</v>
+        <v>115</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J19" t="s">
-        <v>309</v>
+        <v>148</v>
+      </c>
+      <c r="K19" t="s">
+        <v>372</v>
+      </c>
+      <c r="L19" t="s">
+        <v>373</v>
+      </c>
+      <c r="M19" t="s">
+        <v>374</v>
+      </c>
+      <c r="N19" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="20">
@@ -2879,28 +3318,40 @@
         <v>185</v>
       </c>
       <c r="C20" t="s">
-        <v>310</v>
+        <v>376</v>
       </c>
       <c r="D20" t="s">
-        <v>311</v>
+        <v>377</v>
       </c>
       <c r="E20" t="s">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="F20" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="G20" t="s">
-        <v>314</v>
+        <v>379</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s">
         <v>77</v>
       </c>
       <c r="J20" t="s">
-        <v>315</v>
+        <v>380</v>
+      </c>
+      <c r="K20" t="s">
+        <v>381</v>
+      </c>
+      <c r="L20" t="s">
+        <v>382</v>
+      </c>
+      <c r="M20" t="s">
+        <v>383</v>
+      </c>
+      <c r="N20" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
